--- a/Final_Jobs.xlsx
+++ b/Final_Jobs.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,12 +17,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -43,17 +50,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -424,7 +434,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -491,9 +501,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -528,9 +538,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
@@ -565,9 +575,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
@@ -602,9 +612,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -639,9 +649,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -676,9 +686,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
@@ -713,9 +723,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -750,9 +760,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
@@ -787,9 +797,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
@@ -824,9 +834,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
@@ -861,9 +871,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
@@ -898,9 +908,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -935,9 +945,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -972,9 +982,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
@@ -1009,9 +1019,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -1046,9 +1056,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
@@ -1083,9 +1093,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
@@ -1120,9 +1130,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
@@ -1157,9 +1167,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
@@ -1194,9 +1204,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
@@ -1231,9 +1241,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -1268,9 +1278,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
@@ -1305,9 +1315,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
@@ -1342,9 +1352,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
@@ -1379,9 +1389,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
@@ -1416,9 +1426,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
@@ -1453,9 +1463,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
@@ -1490,9 +1500,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
@@ -1527,9 +1537,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
@@ -1564,9 +1574,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
@@ -1601,9 +1611,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
@@ -1638,9 +1648,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
@@ -1675,9 +1685,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -1712,9 +1722,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
@@ -1749,9 +1759,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
@@ -1786,9 +1796,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
@@ -1823,9 +1833,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
@@ -1860,9 +1870,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
@@ -1897,9 +1907,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -1934,9 +1944,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
@@ -1971,9 +1981,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
@@ -2008,9 +2018,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
@@ -2045,9 +2055,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
@@ -2082,9 +2092,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
@@ -2119,9 +2129,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
@@ -2156,9 +2166,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
@@ -2193,9 +2203,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
@@ -2230,9 +2240,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
@@ -2267,9 +2277,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
@@ -2304,9 +2314,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
@@ -2341,9 +2351,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -2378,9 +2388,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
@@ -2415,9 +2425,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
@@ -2452,9 +2462,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
@@ -2489,9 +2499,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
@@ -2526,9 +2536,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G57" s="1" t="inlineStr">
@@ -2563,9 +2573,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -2600,9 +2610,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
@@ -2637,9 +2647,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
@@ -2674,9 +2684,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
@@ -2711,9 +2721,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
@@ -2748,9 +2758,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
@@ -2785,9 +2795,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
@@ -2822,9 +2832,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
@@ -2859,9 +2869,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
@@ -2896,9 +2906,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
@@ -2933,9 +2943,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
@@ -2970,9 +2980,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
@@ -3007,9 +3017,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
@@ -3044,9 +3054,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
@@ -3081,9 +3091,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
@@ -3118,9 +3128,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
@@ -3155,9 +3165,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
@@ -3192,9 +3202,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
@@ -3229,9 +3239,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
@@ -3266,9 +3276,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
@@ -3303,9 +3313,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
@@ -3340,9 +3350,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
@@ -3377,9 +3387,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
@@ -3414,9 +3424,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
@@ -3451,9 +3461,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
@@ -3488,9 +3498,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
@@ -3525,9 +3535,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
@@ -3562,9 +3572,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
@@ -3599,9 +3609,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
@@ -3636,9 +3646,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
@@ -3673,9 +3683,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
@@ -3710,9 +3720,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
@@ -3747,9 +3757,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
@@ -3784,9 +3794,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
@@ -3821,9 +3831,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
@@ -3858,9 +3868,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
@@ -3895,9 +3905,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
@@ -3932,9 +3942,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
@@ -3969,9 +3979,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
@@ -4006,9 +4016,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
@@ -4043,9 +4053,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
@@ -4080,9 +4090,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
@@ -4117,9 +4127,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
@@ -4154,9 +4164,9 @@
           <t>Not Disclosed</t>
         </is>
       </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>https://realpython.github.iohttps://www.realpython.com</t>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realpython.com</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
@@ -4166,6 +4176,108 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>